--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0125.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0125.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Trong mơ, ta không bao giờ về được tiền đồn. Ta cứ... mắc kẹt mãi ngoài vùng băng giá. Lặp đi lặp lại... mãi không thoát ra được.</t>
+          <t>Trong mơ, tao không bao giờ về được tiền đồn. Tao cứ... mắc kẹt mãi ngoài vùng băng giá. Lặp đi lặp lại... mãi không thoát ra được.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Ta không quên gì cả... ngoại trừ một phần của chính mình.</t>
+          <t>Tao không quên gì cả... ngoại trừ một phần của chính mình.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Nhưng đống đổ nát này mới được phát hiện vài ngày trước thôi, mà ta chưa bao giờ rời khỏi tiền đồn. Vậy tại sao nó lại... quen thuộc đến thế?</t>
+          <t>Nhưng đống đổ nát này mới được phát hiện vài ngày trước thôi, mà tao chưa bao giờ rời khỏi tiền đồn. Vậy tại sao nó lại... quen thuộc đến thế?</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Có chuyện gì mà cậu lại đến đây?</t>
+          <t>Có chuyện gì mà bạn lại đến đây?</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Ta đang nghỉ phép. Ta muốn vào thăm bên trong trạm vũ trụ. Họ đã cấp giấy phép thăm quan chưa?</t>
+          <t>Tao đang nghỉ phép. Tao muốn vào thăm bên trong trạm vũ trụ. Họ đã cấp giấy phép thăm quan chưa?</t>
         </is>
       </c>
     </row>
